--- a/jogos_2024-11-15.xlsx
+++ b/jogos_2024-11-15.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Quang Nam</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="M2" t="n">
         <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45611.29166666666</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Quang Nam</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="M3" t="n">
         <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="X3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45611.29166666666</v>
@@ -1546,20 +1546,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
         <v>1.57</v>
@@ -1602,53 +1602,53 @@
         <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.5</v>
       </c>
-      <c r="X9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45611.45833333334</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="R10" t="n">
         <v>1.57</v>
@@ -1731,53 +1731,53 @@
         <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['47']</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45611.45833333334</v>
@@ -1794,32 +1794,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA11" t="n">
         <v>5.5</v>
       </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AB11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['2', '25', '72', '84']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45611.66666666666</v>
@@ -1923,32 +1923,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['2', '25', '72', '84']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AI12" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45611.66666666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
         <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
@@ -2118,32 +2118,32 @@
         <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2151,20 +2151,20 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['66', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45611.6875</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Caldiero Terme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.75</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y14" t="n">
         <v>2.3</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Z14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AD14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['55', '82']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['20', '88']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.3</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AI14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45611.6875</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O16" t="n">
         <v>3.25</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.88</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="X16" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['66', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['44', '58']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45611.6875</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
         <v>1.5</v>
@@ -2634,53 +2634,53 @@
         <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="X17" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.19</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45611.6875</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Caldiero Terme</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
+      <c r="Q18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.63</v>
       </c>
-      <c r="M18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
         <v>3.25</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.75</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['44', '58']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['55', '82']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['20', '88']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45611.6875</v>
